--- a/public/downloads/residential.xlsx
+++ b/public/downloads/residential.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="212">
   <si>
     <t>115 年度住宿式長期照顧服務機構績效考核指標自我檢核表</t>
   </si>
@@ -41,7 +41,7 @@
     <t>備註</t>
   </si>
   <si>
-    <t>A1 工作人員權益保障</t>
+    <t>A、經營管理效能</t>
   </si>
   <si>
     <t>A1</t>
@@ -60,9 +60,6 @@
     <t/>
   </si>
   <si>
-    <t>A2 服務對象入出機構作業</t>
-  </si>
-  <si>
     <t>A2</t>
   </si>
   <si>
@@ -76,9 +73,6 @@
 5. 出院（所）後有追蹤訪視紀錄（適用返家或轉介者）</t>
   </si>
   <si>
-    <t>A3 業務計畫訂定與執行</t>
-  </si>
-  <si>
     <t>A3</t>
   </si>
   <si>
@@ -91,9 +85,6 @@
 4. 業務計畫訂定過程有跨部門參與及主管審核簽核</t>
   </si>
   <si>
-    <t>A4 前次評鑑（查核）缺失改善情形</t>
-  </si>
-  <si>
     <t>A4</t>
   </si>
   <si>
@@ -106,9 +97,6 @@
 4. 持續監測改善成效，防止缺失事項再度發生</t>
   </si>
   <si>
-    <t>A5 機構內性騷擾及性侵害事件防治機制</t>
-  </si>
-  <si>
     <t>A5</t>
   </si>
   <si>
@@ -121,9 +109,6 @@
 4. 服務對象發生性騷擾或性侵害事件，依規定辦理通報及後續處理</t>
   </si>
   <si>
-    <t>A6 危機事件及緊急應變處理機制</t>
-  </si>
-  <si>
     <t>A6</t>
   </si>
   <si>
@@ -136,9 +121,6 @@
 4. 定期演練危機應變程序，工作人員熟知各自職責</t>
   </si>
   <si>
-    <t>A7 業務負責人資格及執業情形</t>
-  </si>
-  <si>
     <t>A7</t>
   </si>
   <si>
@@ -149,9 +131,6 @@
 2. 業務負責人實際管理機構業務，有參與服務品質相關會議之紀錄
 3. 業務負責人每月至少一次至機構查看實際照護情形，並有書面紀錄
 4. 業務負責人依規定完成在職教育訓練</t>
-  </si>
-  <si>
-    <t>A8 聘用工作人員（含專任、兼任）設置情形</t>
   </si>
   <si>
     <t>A8</t>
@@ -167,9 +146,6 @@
 5. 廚工及其他工作人員符合業務需求，並依法辦理相關健康檢查</t>
   </si>
   <si>
-    <t>A9 工作人員教育訓練計畫訂定及辦理情形</t>
-  </si>
-  <si>
     <t>A9</t>
   </si>
   <si>
@@ -183,7 +159,7 @@
 5. 教育訓練辦理情形有統計及分析，作為次年度計畫改善依據</t>
   </si>
   <si>
-    <t>B1 服務品質改善會議及檢討機制</t>
+    <t>B、專業照護品質</t>
   </si>
   <si>
     <t>B1</t>
@@ -196,9 +172,6 @@
 2. 會議中提出服務品質指標數據，進行分析與檢討
 3. 會議決議事項有追蹤管考機制及改善成效記錄
 4. 各專業人員（護理、社工、復健、營養）均參與品質改善會議</t>
-  </si>
-  <si>
-    <t>B2 個案服務計畫評值（含社工及護理共同評值）</t>
   </si>
   <si>
     <t>B2</t>
@@ -214,9 +187,6 @@
 5. 抽查服務計畫與實際照護措施之符合程度</t>
   </si>
   <si>
-    <t>B3 新入住服務對象適應輔導</t>
-  </si>
-  <si>
     <t>B3</t>
   </si>
   <si>
@@ -229,9 +199,6 @@
 4. 針對適應困難個案訂有個別化輔導措施</t>
   </si>
   <si>
-    <t>B4 跨專業整合照護服務</t>
-  </si>
-  <si>
     <t>B4</t>
   </si>
   <si>
@@ -244,9 +211,6 @@
 4. 有轉介其他醫療或社會資源之機制，並有轉介記錄</t>
   </si>
   <si>
-    <t>B5 辦理團體活動及社區參與</t>
-  </si>
-  <si>
     <t>B5</t>
   </si>
   <si>
@@ -259,9 +223,6 @@
 4. 辦理生命回顧、懷舊療法或其他促進心理健康之活動</t>
   </si>
   <si>
-    <t>B6 結合社區資源提供服務</t>
-  </si>
-  <si>
     <t>B6</t>
   </si>
   <si>
@@ -274,9 +235,6 @@
 4. 與社區志工組織或宗教團體建立合作關係</t>
   </si>
   <si>
-    <t>B7 促進服務對象與家屬互動</t>
-  </si>
-  <si>
     <t>B7</t>
   </si>
   <si>
@@ -289,9 +247,6 @@
 4. 建立家屬申訴及意見反映管道，並有處理紀錄</t>
   </si>
   <si>
-    <t>B8 例行醫療照護及就醫安排</t>
-  </si>
-  <si>
     <t>B8</t>
   </si>
   <si>
@@ -302,9 +257,6 @@
 2. 慢性病服務對象用藥管理完整，有藥歷及用藥指導紀錄
 3. 安排牙科、眼科等定期檢查，有就醫安排及追蹤紀錄
 4. 護理人員依醫囑確實執行護理處置，有完整護理記錄</t>
-  </si>
-  <si>
-    <t>B9 傳染病防治及感染管制</t>
   </si>
   <si>
     <t>B9</t>
@@ -320,9 +272,6 @@
 5. 備有充足個人防護裝備（口罩、手套、隔離衣等），並有管理機制</t>
   </si>
   <si>
-    <t>B10 處方藥品管理</t>
-  </si>
-  <si>
     <t>B10</t>
   </si>
   <si>
@@ -336,9 +285,6 @@
 5. 藥品有效期限定期檢查，過期藥品依規定處理</t>
   </si>
   <si>
-    <t>B11 藥事照護服務</t>
-  </si>
-  <si>
     <t>B11</t>
   </si>
   <si>
@@ -349,9 +295,6 @@
 2. 服務對象用藥評估，定期檢視多重用藥及潛在不適當用藥
 3. 工作人員接受藥事照護相關教育訓練
 4. 有藥物不良反應通報機制，且有記錄及處理</t>
-  </si>
-  <si>
-    <t>B12 跌倒預防及處理</t>
   </si>
   <si>
     <t>B12</t>
@@ -367,9 +310,6 @@
 5. 跌倒發生率有統計並定期分析，列為品質監測指標</t>
   </si>
   <si>
-    <t>B13 壓力性損傷預防及處理</t>
-  </si>
-  <si>
     <t>B13</t>
   </si>
   <si>
@@ -383,9 +323,6 @@
 5. 壓力性損傷發生率有統計並定期分析，列為品質監測指標</t>
   </si>
   <si>
-    <t>B14 疼痛評估及處理</t>
-  </si>
-  <si>
     <t>B14</t>
   </si>
   <si>
@@ -396,9 +333,6 @@
 2. 有疼痛之個案依評估結果訂定疼痛管理計畫
 3. 疼痛處理介入後追蹤評估效果，並有紀錄
 4. 工作人員接受疼痛評估及管理相關教育訓練</t>
-  </si>
-  <si>
-    <t>B15 身體約束使用管理</t>
   </si>
   <si>
     <t>B15</t>
@@ -414,9 +348,6 @@
 5. 身體約束使用率有統計，並定期檢討降低約束措施</t>
   </si>
   <si>
-    <t>B16 感染事件預防及處理</t>
-  </si>
-  <si>
     <t>B16</t>
   </si>
   <si>
@@ -429,9 +360,6 @@
 4. 感染預防措施教育訓練定期辦理</t>
   </si>
   <si>
-    <t>B17 非計畫性住院管理</t>
-  </si>
-  <si>
     <t>B17</t>
   </si>
   <si>
@@ -444,9 +372,6 @@
 4. 建立與合作醫院之轉介及返院照護連續性機制</t>
   </si>
   <si>
-    <t>B18 非計畫性體重變化管理</t>
-  </si>
-  <si>
     <t>B18</t>
   </si>
   <si>
@@ -457,9 +382,6 @@
 2. 非計畫性體重減輕（1個月超過5%或3個月超過7.5%）有追蹤及介入措施
 3. 非計畫性體重減輕個案有營養評估，並調整飲食計畫
 4. 非計畫性體重變化率有統計，列為品質監測指標</t>
-  </si>
-  <si>
-    <t>B19 管路移除（鼻胃管及導尿管）</t>
   </si>
   <si>
     <t>B19</t>
@@ -475,9 +397,6 @@
 5. 管路移除率有統計，並定期分析</t>
   </si>
   <si>
-    <t>B20 服務對象健康檢查</t>
-  </si>
-  <si>
     <t>B20</t>
   </si>
   <si>
@@ -490,9 +409,6 @@
 4. 新入住服務對象完成基礎健康評估</t>
   </si>
   <si>
-    <t>B21 侵入性照護技術管理</t>
-  </si>
-  <si>
     <t>B21</t>
   </si>
   <si>
@@ -505,9 +421,6 @@
 4. 侵入性照護相關感染事件有監測及改善機制</t>
   </si>
   <si>
-    <t>B22 緊急送醫作業</t>
-  </si>
-  <si>
     <t>B22</t>
   </si>
   <si>
@@ -520,9 +433,6 @@
 4. 緊急送醫事件定期分析，作為預防及改善依據</t>
   </si>
   <si>
-    <t>B23 疫苗注射服務</t>
-  </si>
-  <si>
     <t>B23</t>
   </si>
   <si>
@@ -535,9 +445,6 @@
 4. 有接種禁忌評估，並記錄接種後觀察情形</t>
   </si>
   <si>
-    <t>B24 促進日常活動及下床</t>
-  </si>
-  <si>
     <t>B24</t>
   </si>
   <si>
@@ -550,9 +457,6 @@
 4. 長期臥床個案有預防廢用症候群之計畫及執行記錄</t>
   </si>
   <si>
-    <t>B25 身體清潔及翻身照護</t>
-  </si>
-  <si>
     <t>B25</t>
   </si>
   <si>
@@ -565,9 +469,6 @@
 4. 個人清潔照護尊重服務對象隱私，注意保暖</t>
   </si>
   <si>
-    <t>B26 失禁服務對象定時如廁計畫</t>
-  </si>
-  <si>
     <t>B26</t>
   </si>
   <si>
@@ -580,9 +481,6 @@
 4. 工作人員接受失禁照護及定時如廁計畫相關訓練</t>
   </si>
   <si>
-    <t>B27 自我照顧能力維持及輔具使用</t>
-  </si>
-  <si>
     <t>B27</t>
   </si>
   <si>
@@ -593,9 +491,6 @@
 2. 依評估結果訂定自我照顧能力訓練或維持計畫
 3. 輔具使用依個案需求評估，有輔具清單及使用維護記錄
 4. 服務對象輔具需求有轉介復健治療師評估及建議</t>
-  </si>
-  <si>
-    <t>B28 膳食及個別化飲食照護</t>
   </si>
   <si>
     <t>B28</t>
@@ -611,9 +506,6 @@
 5. 服務對象飲食照護有紀錄，包含進食量評估及異常狀況處理</t>
   </si>
   <si>
-    <t>B29 管灌飲食照護</t>
-  </si>
-  <si>
     <t>B29</t>
   </si>
   <si>
@@ -626,7 +518,7 @@
 4. 管灌操作由具備能力之護理人員或經訓練之照服員執行</t>
   </si>
   <si>
-    <t>C1 建築物安全維護</t>
+    <t>C、安全環境設備</t>
   </si>
   <si>
     <t>C1</t>
@@ -641,9 +533,6 @@
 4. 無障礙設施設置完整，符合服務對象行動需求</t>
   </si>
   <si>
-    <t>C2 寢室及生活空間環境管理</t>
-  </si>
-  <si>
     <t>C2</t>
   </si>
   <si>
@@ -656,9 +545,6 @@
 4. 生活輔助設施（扶手、防滑墊、呼叫系統等）設置完整且功能正常</t>
   </si>
   <si>
-    <t>C3 浴廁及盥洗設備安全</t>
-  </si>
-  <si>
     <t>C3</t>
   </si>
   <si>
@@ -671,9 +557,6 @@
 4. 服務對象如廁或沐浴時工作人員給予適當協助，保護隱私</t>
   </si>
   <si>
-    <t>C4 餐廳及廚房衛生管理</t>
-  </si>
-  <si>
     <t>C4</t>
   </si>
   <si>
@@ -686,9 +569,6 @@
 4. 餐廳環境整潔，桌椅適合服務對象使用</t>
   </si>
   <si>
-    <t>C5 污物及廢棄物處理</t>
-  </si>
-  <si>
     <t>C5</t>
   </si>
   <si>
@@ -701,9 +581,6 @@
 4. 廢水排放符合環境保護規定</t>
   </si>
   <si>
-    <t>C6 藥品及醫療器材安全管理</t>
-  </si>
-  <si>
     <t>C6</t>
   </si>
   <si>
@@ -716,9 +593,6 @@
 4. 氧氣設備（如使用）依規定儲存及管理</t>
   </si>
   <si>
-    <t>C7 電梯及機械升降設備安全</t>
-  </si>
-  <si>
     <t>C7</t>
   </si>
   <si>
@@ -730,9 +604,6 @@
 3. 其他機械升降設備（如升降台）定期維護保養，有紀錄</t>
   </si>
   <si>
-    <t>C8 緊急發電及停電應變</t>
-  </si>
-  <si>
     <t>C8</t>
   </si>
   <si>
@@ -742,9 +613,6 @@
     <t xml:space="preserve">1. 設有緊急發電設備，定期試運轉並有紀錄
 2. 停電應變計畫訂定完整，工作人員熟知停電處理程序
 3. 停電時需持續電力供應之醫療設備（如氧氣機、電動床）有備用方案</t>
-  </si>
-  <si>
-    <t>C9 用電安全及消防管理</t>
   </si>
   <si>
     <t>C9</t>
@@ -760,9 +628,6 @@
 5. 消防安全設備定期委由消防設備師（士）檢修，有報告書</t>
   </si>
   <si>
-    <t>C10 等待救援空間設置</t>
-  </si>
-  <si>
     <t>C10</t>
   </si>
   <si>
@@ -775,9 +640,6 @@
 4. 等待救援空間定期辦理功能測試，確保可使用狀態</t>
   </si>
   <si>
-    <t>C11 緊急應變（EOP）演練</t>
-  </si>
-  <si>
     <t>C11</t>
   </si>
   <si>
@@ -790,9 +652,6 @@
 4. 演練紀錄完整，包含參與人員、演練情境、執行情形及檢討結論</t>
   </si>
   <si>
-    <t>C12 疏散策略及持續照護作業程序</t>
-  </si>
-  <si>
     <t>C12</t>
   </si>
   <si>
@@ -805,9 +664,6 @@
 4. 工作人員接受疏散策略教育訓練並有紀錄；實地抽測工作人員執行疏散之能力</t>
   </si>
   <si>
-    <t>C13 情境式火災風險辨識與疏散演練</t>
-  </si>
-  <si>
     <t>C13</t>
   </si>
   <si>
@@ -820,9 +676,6 @@
 4. 情境演練評估紀錄完整，有後續改善追蹤</t>
   </si>
   <si>
-    <t>C14 疏散避難通道及設施維護</t>
-  </si>
-  <si>
     <t>C14</t>
   </si>
   <si>
@@ -835,9 +688,6 @@
 4. 服務對象床位配置合理，利於緊急疏散作業</t>
   </si>
   <si>
-    <t>C15 物理環境安全及無障礙設施</t>
-  </si>
-  <si>
     <t>C15</t>
   </si>
   <si>
@@ -850,9 +700,6 @@
 4. 戶外活動空間安全維護，定期檢查</t>
   </si>
   <si>
-    <t>C16 輔具與移位設備安全管理</t>
-  </si>
-  <si>
     <t>C16</t>
   </si>
   <si>
@@ -865,7 +712,7 @@
 4. 機構備有足夠之移位及照護輔具，供服務對象使用</t>
   </si>
   <si>
-    <t>D1 服務對象人身安全及尊嚴維護</t>
+    <t>D、個案權益保障</t>
   </si>
   <si>
     <t>D1</t>
@@ -878,9 +725,6 @@
 2. 禁止對服務對象有任何形式之虐待、疏忽或不當對待，有申訴及通報機制
 3. 服務對象遭受不當對待之事件依規定通報並有處理紀錄
 4. 工作人員接受人身安全及尊嚴維護相關教育訓練</t>
-  </si>
-  <si>
-    <t>D2 入住契約及服務說明</t>
   </si>
   <si>
     <t>D2</t>
@@ -896,9 +740,6 @@
 5. 服務對象及家屬對服務內容有知情同意之紀錄</t>
   </si>
   <si>
-    <t>D3 服務對象隱私及個人資料保護</t>
-  </si>
-  <si>
     <t>D3</t>
   </si>
   <si>
@@ -911,9 +752,6 @@
 4. 個案紀錄妥善保管，防止未授權人員取閱</t>
   </si>
   <si>
-    <t>D4 服務對象申訴及意見處理機制</t>
-  </si>
-  <si>
     <t>D4</t>
   </si>
   <si>
@@ -926,9 +764,6 @@
 4. 服務對象意見反映後有追蹤改善，避免申訴事件重複發生</t>
   </si>
   <si>
-    <t>D5 服務對象自主選擇及參與決策</t>
-  </si>
-  <si>
     <t>D5</t>
   </si>
   <si>
@@ -941,9 +776,6 @@
 4. 具認知障礙之服務對象仍依其能力維持最大程度之自主</t>
   </si>
   <si>
-    <t>D6 服務對象居家情境及監視設備管理</t>
-  </si>
-  <si>
     <t>D6</t>
   </si>
   <si>
@@ -956,9 +788,6 @@
 4. 監視或偵測設備不得侵害服務對象隱私（如浴廁、更衣室禁止設置）</t>
   </si>
   <si>
-    <t>D7 服務對象財物及遺物管理</t>
-  </si>
-  <si>
     <t>D7</t>
   </si>
   <si>
@@ -969,9 +798,6 @@
 2. 服務對象死亡後遺物有清點清冊，依規定聯絡家屬辦理
 3. 無家屬或家屬失聯之服務對象，機構協助建立家屬關係並辦理遺物管理，有完整紀錄
 4. 財物管理過程透明，防止糾紛或不當使用</t>
-  </si>
-  <si>
-    <t>D8 安寧緩和醫療及病人自主權利</t>
   </si>
   <si>
     <t>D8</t>
@@ -987,9 +813,6 @@
 5. 建立安寧緩和醫療轉介機制，與醫療機構有合作關係</t>
   </si>
   <si>
-    <t>D9 服務對象宗教信仰及文化需求</t>
-  </si>
-  <si>
     <t>D9</t>
   </si>
   <si>
@@ -1001,7 +824,7 @@
 3. 工作人員接受文化敏感度及多元文化照護相關訓練</t>
   </si>
   <si>
-    <t>加分① 創新或配合政策執行</t>
+    <t>加減分項目</t>
   </si>
   <si>
     <t>加分①</t>
@@ -1016,9 +839,6 @@
 4. 鼓勵工作人員參與創新服務發展，提升服務品質</t>
   </si>
   <si>
-    <t>加分② 機構內空氣品質管理</t>
-  </si>
-  <si>
     <t>加分②</t>
   </si>
   <si>
@@ -1029,9 +849,6 @@
 2. 有室內空氣品質監測紀錄，含監測日期、地點及數值
 3. 空氣品質不符標準時，有通風改善措施及後續追蹤紀錄
 4. 機構說明改善室內空氣品質之具體作法（如加強通風換氣、空氣清淨機設置等）</t>
-  </si>
-  <si>
-    <t>扣分③ 評鑑期間之違規及重大負面事件</t>
   </si>
   <si>
     <t>扣分③</t>
@@ -1463,7 +1280,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1542,26 +1359,38 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+    <row r="5" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-    </row>
-    <row r="6" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>12</v>
@@ -1576,26 +1405,38 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
+    <row r="7" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="8" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>12</v>
@@ -1610,26 +1451,38 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
+    <row r="9" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="10" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>12</v>
@@ -1644,26 +1497,38 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-    </row>
-    <row r="12" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>12</v>
@@ -1678,154 +1543,10 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-    </row>
-    <row r="14" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-    </row>
-    <row r="16" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-    </row>
-    <row r="18" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-    </row>
-    <row r="20" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="2">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A19:G19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1834,7 +1555,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1881,7 +1602,7 @@
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -1892,141 +1613,189 @@
     </row>
     <row r="4" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="D6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="B7" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="C7" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-    </row>
-    <row r="6" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
+      <c r="D7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="8" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="C9" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
+      <c r="D9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="10" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="D10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="B11" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="C11" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-    </row>
-    <row r="12" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>62</v>
       </c>
@@ -2049,26 +1818,38 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+    <row r="13" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
+      <c r="B13" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="14" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>12</v>
@@ -2083,26 +1864,38 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-    </row>
-    <row r="16" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>12</v>
@@ -2117,26 +1910,38 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-    </row>
-    <row r="18" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>12</v>
@@ -2151,26 +1956,38 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-    </row>
-    <row r="20" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>12</v>
@@ -2185,26 +2002,38 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
+    <row r="21" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="22" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>12</v>
@@ -2219,26 +2048,38 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
+    <row r="23" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="24" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>12</v>
@@ -2253,26 +2094,38 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-    </row>
-    <row r="26" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>12</v>
@@ -2287,26 +2140,38 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-    </row>
-    <row r="28" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>12</v>
@@ -2321,26 +2186,38 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
+    <row r="29" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="30" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>12</v>
@@ -2355,26 +2232,38 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-    </row>
-    <row r="32" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>12</v>
@@ -2389,514 +2278,10 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-    </row>
-    <row r="34" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="35" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-    </row>
-    <row r="36" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G36" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
-    </row>
-    <row r="38" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F38" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="39" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
-    </row>
-    <row r="40" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F40" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G40" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="41" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="B41" s="3"/>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
-    </row>
-    <row r="42" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F42" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G42" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="43" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3"/>
-    </row>
-    <row r="44" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G44" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="45" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
-    </row>
-    <row r="46" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F46" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G46" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="47" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="B47" s="3"/>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
-    </row>
-    <row r="48" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F48" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G48" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="49" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
-    </row>
-    <row r="50" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F50" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G50" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="51" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
-      <c r="E51" s="3"/>
-      <c r="F51" s="3"/>
-      <c r="G51" s="3"/>
-    </row>
-    <row r="52" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E52" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F52" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G52" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="53" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
-      <c r="E53" s="3"/>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3"/>
-    </row>
-    <row r="54" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F54" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G54" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="55" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
-      <c r="E55" s="3"/>
-      <c r="F55" s="3"/>
-      <c r="G55" s="3"/>
-    </row>
-    <row r="56" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E56" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F56" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G56" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="57" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="B57" s="3"/>
-      <c r="C57" s="3"/>
-      <c r="D57" s="3"/>
-      <c r="E57" s="3"/>
-      <c r="F57" s="3"/>
-      <c r="G57" s="3"/>
-    </row>
-    <row r="58" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E58" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F58" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G58" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="59" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="B59" s="3"/>
-      <c r="C59" s="3"/>
-      <c r="D59" s="3"/>
-      <c r="E59" s="3"/>
-      <c r="F59" s="3"/>
-      <c r="G59" s="3"/>
-    </row>
-    <row r="60" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E60" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F60" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G60" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="2">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A33:G33"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A37:G37"/>
-    <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A41:G41"/>
-    <mergeCell ref="A43:G43"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="A47:G47"/>
-    <mergeCell ref="A49:G49"/>
-    <mergeCell ref="A51:G51"/>
-    <mergeCell ref="A53:G53"/>
-    <mergeCell ref="A55:G55"/>
-    <mergeCell ref="A57:G57"/>
-    <mergeCell ref="A59:G59"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -2905,7 +2290,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2952,7 +2337,7 @@
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>161</v>
+        <v>125</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -2963,13 +2348,13 @@
     </row>
     <row r="4" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>162</v>
+        <v>126</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>163</v>
+        <v>127</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>164</v>
+        <v>128</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>12</v>
@@ -2984,26 +2369,38 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
+    <row r="5" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="6" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>166</v>
+        <v>132</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>167</v>
+        <v>133</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>12</v>
@@ -3018,26 +2415,38 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
+    <row r="7" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="8" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>170</v>
+        <v>138</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>12</v>
@@ -3052,26 +2461,38 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-    </row>
-    <row r="10" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>174</v>
+        <v>144</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>175</v>
+        <v>145</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>176</v>
+        <v>146</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>12</v>
@@ -3086,26 +2507,38 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-    </row>
-    <row r="12" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" ht="48" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>178</v>
+        <v>150</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>12</v>
@@ -3120,26 +2553,38 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
+    <row r="13" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="14" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>182</v>
+        <v>156</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>183</v>
+        <v>157</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>12</v>
@@ -3154,26 +2599,38 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-    </row>
-    <row r="16" ht="48" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>12</v>
@@ -3188,26 +2645,38 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-    </row>
-    <row r="18" ht="48" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>190</v>
+        <v>168</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>191</v>
+        <v>169</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>192</v>
+        <v>170</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>12</v>
@@ -3222,297 +2691,33 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-    </row>
-    <row r="20" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-    </row>
-    <row r="22" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-    </row>
-    <row r="24" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-    </row>
-    <row r="26" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-    </row>
-    <row r="28" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-    </row>
-    <row r="30" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="31" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-    </row>
-    <row r="32" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-    </row>
-    <row r="34" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G34" s="5" t="s">
+    <row r="19" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="5" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="2">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A33:G33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3521,7 +2726,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3568,7 +2773,7 @@
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>225</v>
+        <v>174</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -3579,13 +2784,13 @@
     </row>
     <row r="4" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>226</v>
+        <v>175</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>227</v>
+        <v>176</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>228</v>
+        <v>177</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>12</v>
@@ -3600,26 +2805,38 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-    </row>
-    <row r="6" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>230</v>
+        <v>181</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>231</v>
+        <v>182</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>232</v>
+        <v>183</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>12</v>
@@ -3634,26 +2851,38 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
+    <row r="7" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="8" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>234</v>
+        <v>187</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>235</v>
+        <v>188</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>12</v>
@@ -3668,26 +2897,38 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
+    <row r="9" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="10" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>238</v>
+        <v>193</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>239</v>
+        <v>194</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>240</v>
+        <v>195</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>12</v>
@@ -3702,26 +2943,38 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-    </row>
-    <row r="12" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>242</v>
+        <v>199</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>243</v>
+        <v>200</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>244</v>
+        <v>201</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>12</v>
@@ -3736,154 +2989,10 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-    </row>
-    <row r="14" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-    </row>
-    <row r="16" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-    </row>
-    <row r="18" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-    </row>
-    <row r="20" ht="48" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="2">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A19:G19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3892,7 +3001,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3939,7 +3048,7 @@
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>261</v>
+        <v>202</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -3950,13 +3059,13 @@
     </row>
     <row r="4" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>262</v>
+        <v>203</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>263</v>
+        <v>204</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>264</v>
+        <v>205</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>12</v>
@@ -3971,26 +3080,38 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
+    <row r="5" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="6" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>266</v>
+        <v>209</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>267</v>
+        <v>210</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>268</v>
+        <v>211</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>12</v>
@@ -4005,46 +3126,10 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-    </row>
-    <row r="8" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="2">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A7:G7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
